--- a/outputs_xlsx_solution/test33.1-wide.xlsx
+++ b/outputs_xlsx_solution/test33.1-wide.xlsx
@@ -125,6 +125,9 @@
     <t>fadd F22, F20, F22</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -1287,6 +1293,12 @@
       <c r="Q13" t="s">
         <v>21</v>
       </c>
+      <c r="X13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>30</v>
+      </c>
       <c r="Z13" t="s">
         <v>8</v>
       </c>
@@ -1521,13 +1533,22 @@
         <v>6</v>
       </c>
       <c r="X20" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA20" t="s">
         <v>30</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="AB20" t="s">
         <v>30</v>
       </c>
-      <c r="Z20" t="s">
-        <v>21</v>
+      <c r="AC20" t="s">
+        <v>30</v>
       </c>
       <c r="AD20" t="s">
         <v>8</v>
@@ -1591,7 +1612,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X22" t="s">
         <v>5</v>
@@ -1620,7 +1641,7 @@
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y23" t="s">
         <v>5</v>
@@ -1649,7 +1670,7 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="s">
         <v>5</v>
@@ -1780,7 +1801,7 @@
         <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AI28" t="s">
         <v>5</v>
@@ -1812,7 +1833,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ29" t="s">
         <v>5</v>
@@ -1841,7 +1862,7 @@
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="s">
         <v>5</v>
@@ -1972,7 +1993,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AO34" t="s">
         <v>5</v>
@@ -2001,7 +2022,7 @@
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AP35" t="s">
         <v>5</v>
@@ -2030,7 +2051,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AQ36" t="s">
         <v>5</v>
@@ -2059,7 +2080,7 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AU37" t="s">
         <v>5</v>
@@ -2094,7 +2115,7 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AV38" t="s">
         <v>5</v>
@@ -2129,7 +2150,7 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AW39" t="s">
         <v>5</v>
@@ -2155,7 +2176,7 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AX40" t="s">
         <v>5</v>
@@ -2187,7 +2208,7 @@
         <v>6</v>
       </c>
       <c r="BA41" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BB41" t="s">
         <v>8</v>
@@ -2262,6 +2283,12 @@
       <c r="BC43" t="s">
         <v>21</v>
       </c>
+      <c r="BJ43" t="s">
+        <v>30</v>
+      </c>
+      <c r="BK43" t="s">
+        <v>30</v>
+      </c>
       <c r="BL43" t="s">
         <v>8</v>
       </c>
@@ -2496,13 +2523,22 @@
         <v>6</v>
       </c>
       <c r="BJ50" t="s">
+        <v>31</v>
+      </c>
+      <c r="BK50" t="s">
+        <v>31</v>
+      </c>
+      <c r="BL50" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM50" t="s">
         <v>30</v>
       </c>
-      <c r="BK50" t="s">
+      <c r="BN50" t="s">
         <v>30</v>
       </c>
-      <c r="BL50" t="s">
-        <v>21</v>
+      <c r="BO50" t="s">
+        <v>30</v>
       </c>
       <c r="BP50" t="s">
         <v>8</v>
@@ -2569,7 +2605,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BJ52" t="s">
         <v>5</v>
@@ -2598,7 +2634,7 @@
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BK53" t="s">
         <v>5</v>
@@ -2627,7 +2663,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BL54" t="s">
         <v>5</v>
@@ -2696,6 +2732,9 @@
       <c r="BR56" t="s">
         <v>21</v>
       </c>
+      <c r="BS56" t="s">
+        <v>30</v>
+      </c>
       <c r="BT56" t="s">
         <v>8</v>
       </c>
@@ -2764,7 +2803,7 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BP58" t="s">
         <v>5</v>
@@ -2799,7 +2838,7 @@
         <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BQ59" t="s">
         <v>5</v>
@@ -2828,7 +2867,7 @@
         <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BR60" t="s">
         <v>5</v>
@@ -2894,6 +2933,9 @@
       <c r="BX62" t="s">
         <v>21</v>
       </c>
+      <c r="BY62" t="s">
+        <v>30</v>
+      </c>
       <c r="BZ62" t="s">
         <v>8</v>
       </c>
@@ -2959,16 +3001,16 @@
         <v>80</v>
       </c>
       <c r="C64" t="s">
+        <v>32</v>
+      </c>
+      <c r="BV64" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW64" t="s">
+        <v>6</v>
+      </c>
+      <c r="BZ64" t="s">
         <v>31</v>
-      </c>
-      <c r="BV64" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW64" t="s">
-        <v>6</v>
-      </c>
-      <c r="BZ64" t="s">
-        <v>30</v>
       </c>
       <c r="CA64" t="s">
         <v>21</v>
@@ -2991,7 +3033,7 @@
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BW65" t="s">
         <v>5</v>
@@ -3020,7 +3062,7 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BX66" t="s">
         <v>5</v>
@@ -3049,7 +3091,7 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CE67" t="s">
         <v>5</v>
@@ -3084,7 +3126,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CF68" t="s">
         <v>5</v>
@@ -3119,7 +3161,7 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CG69" t="s">
         <v>5</v>
@@ -3145,7 +3187,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CH70" t="s">
         <v>5</v>
@@ -3180,7 +3222,7 @@
         <v>6</v>
       </c>
       <c r="CK71" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="CL71" t="s">
         <v>8</v>
@@ -3258,6 +3300,12 @@
       <c r="CM73" t="s">
         <v>21</v>
       </c>
+      <c r="CT73" t="s">
+        <v>30</v>
+      </c>
+      <c r="CU73" t="s">
+        <v>30</v>
+      </c>
       <c r="CV73" t="s">
         <v>8</v>
       </c>
@@ -3492,13 +3540,22 @@
         <v>6</v>
       </c>
       <c r="CT80" t="s">
+        <v>31</v>
+      </c>
+      <c r="CU80" t="s">
+        <v>31</v>
+      </c>
+      <c r="CV80" t="s">
+        <v>21</v>
+      </c>
+      <c r="CW80" t="s">
         <v>30</v>
       </c>
-      <c r="CU80" t="s">
+      <c r="CX80" t="s">
         <v>30</v>
       </c>
-      <c r="CV80" t="s">
-        <v>21</v>
+      <c r="CY80" t="s">
+        <v>30</v>
       </c>
       <c r="CZ80" t="s">
         <v>8</v>
@@ -3565,7 +3622,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CT82" t="s">
         <v>5</v>
@@ -3594,7 +3651,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CU83" t="s">
         <v>5</v>
@@ -3623,7 +3680,7 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CV84" t="s">
         <v>5</v>
@@ -3692,6 +3749,9 @@
       <c r="DB86" t="s">
         <v>21</v>
       </c>
+      <c r="DC86" t="s">
+        <v>30</v>
+      </c>
       <c r="DD86" t="s">
         <v>8</v>
       </c>
@@ -3760,7 +3820,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CZ88" t="s">
         <v>5</v>
@@ -3795,7 +3855,7 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DA89" t="s">
         <v>5</v>
@@ -3824,7 +3884,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DB90" t="s">
         <v>5</v>
@@ -3890,6 +3950,9 @@
       <c r="DH92" t="s">
         <v>21</v>
       </c>
+      <c r="DI92" t="s">
+        <v>30</v>
+      </c>
       <c r="DJ92" t="s">
         <v>8</v>
       </c>
@@ -3955,16 +4018,16 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
+        <v>32</v>
+      </c>
+      <c r="DF94" t="s">
+        <v>5</v>
+      </c>
+      <c r="DG94" t="s">
+        <v>6</v>
+      </c>
+      <c r="DJ94" t="s">
         <v>31</v>
-      </c>
-      <c r="DF94" t="s">
-        <v>5</v>
-      </c>
-      <c r="DG94" t="s">
-        <v>6</v>
-      </c>
-      <c r="DJ94" t="s">
-        <v>30</v>
       </c>
       <c r="DK94" t="s">
         <v>21</v>
@@ -3987,7 +4050,7 @@
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DG95" t="s">
         <v>5</v>
@@ -4016,7 +4079,7 @@
         <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DH96" t="s">
         <v>5</v>
@@ -4045,7 +4108,7 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DO97" t="s">
         <v>5</v>
@@ -4080,7 +4143,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP98" t="s">
         <v>5</v>
@@ -4115,7 +4178,7 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="DQ99" t="s">
         <v>5</v>
@@ -4141,7 +4204,7 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="DR100" t="s">
         <v>5</v>
@@ -4164,7 +4227,7 @@
         <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="DS101" t="s">
         <v>5</v>
@@ -4190,7 +4253,7 @@
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DT102" t="s">
         <v>5</v>
@@ -4216,7 +4279,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="DU103" t="s">
         <v>5</v>
@@ -4245,7 +4308,7 @@
         <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DV104" t="s">
         <v>5</v>
@@ -4289,7 +4352,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="DW105" t="s">
         <v>5</v>
@@ -4315,7 +4378,7 @@
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="DX106" t="s">
         <v>5</v>
@@ -4341,7 +4404,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DY107" t="s">
         <v>5</v>
@@ -4367,7 +4430,7 @@
         <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="DZ108" t="s">
         <v>5</v>
@@ -4393,7 +4456,7 @@
         <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="EA109" t="s">
         <v>5</v>
@@ -4413,7 +4476,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112">
@@ -4421,7 +4484,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113">
@@ -4429,7 +4492,7 @@
         <v>6</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="114">
@@ -4437,7 +4500,7 @@
         <v>21</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115">
@@ -4445,7 +4508,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116">
@@ -4453,7 +4516,7 @@
         <v>10</v>
       </c>
       <c r="B116" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
@@ -4461,23 +4524,39 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B119" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>26</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>30</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
